--- a/PMS.UI/wwwroot/temp/Rota.xlsx
+++ b/PMS.UI/wwwroot/temp/Rota.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Payroll Documents\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noman.yousaf\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C69BFC-D73F-4F78-BBE9-5C5AE976BC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363FB4B1-D51B-4AC9-83D2-074044D3D116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -480,7 +480,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B2">
         <v>1189</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B3">
         <v>1333</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B4">
         <v>1151</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B5">
         <v>1191</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B6">
         <v>1102</v>
@@ -565,7 +565,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B7">
         <v>1072</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B8">
         <v>1217</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B9">
         <v>1047</v>
@@ -616,7 +616,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B10">
         <v>1275</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B11">
         <v>1163</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B12">
         <v>1202</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B13">
         <v>1316</v>
@@ -684,7 +684,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B14">
         <v>1129</v>
@@ -701,7 +701,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B15">
         <v>1239</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B16">
         <v>1138</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46157</v>
+        <v>46222</v>
       </c>
       <c r="B17">
         <v>1112</v>
